--- a/SR-dev/metadata/ontologies-skos-play.xlsx
+++ b/SR-dev/metadata/ontologies-skos-play.xlsx
@@ -1,23 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aschiltz003\Documents\GitHub\EU-wide-Registry-of-Semantic-Models\SR-dev\metadata\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00015771-847C-417A-A4EC-3644DB51114A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="6"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Asset" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="Agent" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="Class" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="ContactPoint" sheetId="4" state="visible" r:id="rId6"/>
-    <sheet name="Document" sheetId="5" state="visible" r:id="rId7"/>
-    <sheet name="Location" sheetId="6" state="visible" r:id="rId8"/>
-    <sheet name="AssetDistribution" sheetId="7" state="visible" r:id="rId9"/>
-    <sheet name="Concept" sheetId="8" state="visible" r:id="rId10"/>
+    <sheet name="Asset" sheetId="1" r:id="rId1"/>
+    <sheet name="Agent" sheetId="2" r:id="rId2"/>
+    <sheet name="Class" sheetId="3" r:id="rId3"/>
+    <sheet name="ContactPoint" sheetId="4" r:id="rId4"/>
+    <sheet name="Document" sheetId="5" r:id="rId5"/>
+    <sheet name="Location" sheetId="6" r:id="rId6"/>
+    <sheet name="AssetDistribution" sheetId="7" r:id="rId7"/>
+    <sheet name="Concept" sheetId="8" r:id="rId8"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="0" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -26,1333 +31,1310 @@
 </workbook>
 </file>
 
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <authors>
-    <author>tc={69670AD0-6484-4FFE-A455-3E1E94647EC3}</author>
-  </authors>
-  <commentList>
-    <comment ref="K19" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    To be added</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1115" uniqueCount="430">
-  <si>
-    <t xml:space="preserve">ConceptScheme URI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://www.w3.org/ns/adms#Asset</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PREFIX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">adms</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://www.w3.org/ns/adms#</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cb</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://publications.europa.eu/resource/authority/corporate-body/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://data.europa.eu/m8g/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dcat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://www.w3.org/ns/dcat#</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dct</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://purl.org/dc/terms/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">foaf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://xmlns.com/foaf/0.1/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">owl</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://www.w3.org/2002/07/owl#</t>
-  </si>
-  <si>
-    <t xml:space="preserve">prof</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://www.w3.org/ns/dx/prof/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://www.w3.org/1999/02/22-rdf-syntax-ns#</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vann</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://purl.org/vocab/vann/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">xsd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://www.w3.org/2001/XMLSchema#</t>
-  </si>
-  <si>
-    <t xml:space="preserve">org</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://www.w3.org/ns/org#</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vcard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://www.w3.org/2006/vcard/ns#</t>
-  </si>
-  <si>
-    <t xml:space="preserve">skos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://www.w3.org/2004/02/skos/core#</t>
-  </si>
-  <si>
-    <t xml:space="preserve">URI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cv:contactPoint</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dct:contributor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dct:creator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dct:created^^xsd:dateTime</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dct:issued</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dct:modified</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dct:description@en</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cv:hasImplementation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dcat:distribution</t>
-  </si>
-  <si>
-    <t xml:space="preserve">foaf:homepage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dct:identifier^^xsd:string</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cv:isReusedBy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dcat:keyword</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dct:language</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cv:lovRank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vann:preferredNamespaceUri</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dct:publisher</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dct:requires</t>
-  </si>
-  <si>
-    <t xml:space="preserve">adms:status</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dcat:theme</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dct:title@en</t>
-  </si>
-  <si>
-    <t xml:space="preserve">owl:versionInfo^^xsd:string</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rdf:type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://www.w3.org/data#W3C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DCAT is an RDF vocabulary designed to facilitate interoperability between data catalogs published on the Web. By using DCAT to describe datasets in data catalogs, publishers increase discoverability and enable applications easily to consume metadata from multiple catalogs. It further enables decentralized publishing of catalogs and facilitates federated dataset search across sites. Aggregated DCAT metadata can serve as a manifest file to facilitate digital preservation. DCAT is defined at http://www.w3.org/TR/vocab-dcat/. Any variance between that normative document and this schema is an error in this schema.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.w3.org/ns/dcat3.ttl</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.w3.org/TR/vocab-dcat-3/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DCAT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://publications.europa.eu/resource/authority/language/ENG</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1115" uniqueCount="431">
+  <si>
+    <t>ConceptScheme URI</t>
+  </si>
+  <si>
+    <t>http://www.w3.org/ns/adms#Asset</t>
+  </si>
+  <si>
+    <t>PREFIX</t>
+  </si>
+  <si>
+    <t>adms</t>
+  </si>
+  <si>
+    <t>http://www.w3.org/ns/adms#</t>
+  </si>
+  <si>
+    <t>cb</t>
+  </si>
+  <si>
+    <t>http://publications.europa.eu/resource/authority/corporate-body/</t>
+  </si>
+  <si>
+    <t>cv</t>
+  </si>
+  <si>
+    <t>http://data.europa.eu/m8g/</t>
+  </si>
+  <si>
+    <t>dcat</t>
+  </si>
+  <si>
+    <t>http://www.w3.org/ns/dcat#</t>
+  </si>
+  <si>
+    <t>dct</t>
+  </si>
+  <si>
+    <t>http://purl.org/dc/terms/</t>
+  </si>
+  <si>
+    <t>foaf</t>
+  </si>
+  <si>
+    <t>http://xmlns.com/foaf/0.1/</t>
+  </si>
+  <si>
+    <t>owl</t>
+  </si>
+  <si>
+    <t>http://www.w3.org/2002/07/owl#</t>
+  </si>
+  <si>
+    <t>prof</t>
+  </si>
+  <si>
+    <t>http://www.w3.org/ns/dx/prof/</t>
+  </si>
+  <si>
+    <t>rdf</t>
+  </si>
+  <si>
+    <t>http://www.w3.org/1999/02/22-rdf-syntax-ns#</t>
+  </si>
+  <si>
+    <t>vann</t>
+  </si>
+  <si>
+    <t>http://purl.org/vocab/vann/</t>
+  </si>
+  <si>
+    <t>xsd</t>
+  </si>
+  <si>
+    <t>http://www.w3.org/2001/XMLSchema#</t>
+  </si>
+  <si>
+    <t>org</t>
+  </si>
+  <si>
+    <t>http://www.w3.org/ns/org#</t>
+  </si>
+  <si>
+    <t>vcard</t>
+  </si>
+  <si>
+    <t>http://www.w3.org/2006/vcard/ns#</t>
+  </si>
+  <si>
+    <t>skos</t>
+  </si>
+  <si>
+    <t>http://www.w3.org/2004/02/skos/core#</t>
+  </si>
+  <si>
+    <t>URI</t>
+  </si>
+  <si>
+    <t>cv:contactPoint</t>
+  </si>
+  <si>
+    <t>dct:contributor</t>
+  </si>
+  <si>
+    <t>dct:creator</t>
+  </si>
+  <si>
+    <t>dct:created^^xsd:dateTime</t>
+  </si>
+  <si>
+    <t>dct:issued</t>
+  </si>
+  <si>
+    <t>dct:modified</t>
+  </si>
+  <si>
+    <t>dct:description@en</t>
+  </si>
+  <si>
+    <t>cv:hasImplementation</t>
+  </si>
+  <si>
+    <t>dcat:distribution</t>
+  </si>
+  <si>
+    <t>foaf:homepage</t>
+  </si>
+  <si>
+    <t>dct:identifier^^xsd:string</t>
+  </si>
+  <si>
+    <t>cv:isReusedBy</t>
+  </si>
+  <si>
+    <t>dcat:keyword</t>
+  </si>
+  <si>
+    <t>dct:language</t>
+  </si>
+  <si>
+    <t>cv:lovRank</t>
+  </si>
+  <si>
+    <t>vann:preferredNamespaceUri</t>
+  </si>
+  <si>
+    <t>dct:publisher</t>
+  </si>
+  <si>
+    <t>dct:requires</t>
+  </si>
+  <si>
+    <t>adms:status</t>
+  </si>
+  <si>
+    <t>dcat:theme</t>
+  </si>
+  <si>
+    <t>dct:title@en</t>
+  </si>
+  <si>
+    <t>owl:versionInfo^^xsd:string</t>
+  </si>
+  <si>
+    <t>rdf:type</t>
+  </si>
+  <si>
+    <t>http://www.w3.org/data#W3C</t>
+  </si>
+  <si>
+    <t>DCAT is an RDF vocabulary designed to facilitate interoperability between data catalogs published on the Web. By using DCAT to describe datasets in data catalogs, publishers increase discoverability and enable applications easily to consume metadata from multiple catalogs. It further enables decentralized publishing of catalogs and facilitates federated dataset search across sites. Aggregated DCAT metadata can serve as a manifest file to facilitate digital preservation. DCAT is defined at http://www.w3.org/TR/vocab-dcat/. Any variance between that normative document and this schema is an error in this schema.</t>
+  </si>
+  <si>
+    <t>https://www.w3.org/ns/dcat3.ttl</t>
+  </si>
+  <si>
+    <t>https://www.w3.org/TR/vocab-dcat-3/</t>
+  </si>
+  <si>
+    <t>DCAT</t>
+  </si>
+  <si>
+    <t>http://publications.europa.eu/resource/authority/language/ENG</t>
   </si>
   <si>
     <t xml:space="preserve">The data catalog vocabulary </t>
   </si>
   <si>
-    <t xml:space="preserve">3.0.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">adms:Asset</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://danbri.org/foaf.rdf#danbri,http://data.semanticweb.org/person/libby-miller</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FOAF is a project devoted to linking people and information using the Web. Regardless of whether information is in people's heads, in physical or digital documents, or in the form of factual data, it can be linked. FOAF integrates three kinds of network: social networks of human collaboration, friendship and association; representational networks that describe a simplified view of a cartoon universe in factual terms, and information networks that use Web-based linking to share independently published descriptions of this inter-connected world. FOAF does not compete with socially-oriented Web sites; rather it provides an approach in which different sites can tell different parts of the larger story, and by which users can retain some control over their information in a non-proprietary format.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://raw.githubusercontent.com/SEMICeu/EU-wide-Registry-of-Semantic-Models/refs/heads/main/SR-dev/foaf.ttl</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://xmlns.com/foaf/spec/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FOAF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Friend of a Friend (FOAF) vocabulary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.99</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://purl.org/dc/aboutdcmi#DCMI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">This document is an up-to-date specification of all metadata terms maintained by the Dublin Core Metadata Initiative, including properties, vocabulary encoding schemes, syntax encoding schemes, and classes.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.dublincore.org/specifications/dublin-core/dcmi-terms/dublin_core_terms.ttl</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.dublincore.org/specifications/dublin-core/dcmi-terms/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DC Terms</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DCMI Metadata Terms - other</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2020-01-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vocabulary for describing organizational structures, specializable to a broad variety of types of organization.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.w3.org/ns/org.ttl</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.w3.org/TR/vocab-org/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W3C Org</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Core organization ontology</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ontology for vCard based on RFC6350</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.w3.org/2006/vcard/ns#</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.w3.org/TR/vcard-rdf/#Ontology</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W3C vCard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ontology for vCard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Final</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://www.w3.org/2004/02/skos/core</t>
-  </si>
-  <si>
-    <t xml:space="preserve">An RDF vocabulary for describing the basic structure and content of concept schemes such as thesauri, classification schemes, subject heading lists, taxonomies, 'folksonomies', other types of controlled vocabulary, and also concept schemes embedded in glossaries and terminologies.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://raw.githubusercontent.com/SEMICeu/EU-wide-Registry-of-Semantic-Models/refs/heads/main/SR-dev/skos.ttl</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.w3.org/TR/skos-reference/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SKOS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SKOS Vocabulary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20090818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://www.w3.org/2002/07/owl</t>
-  </si>
-  <si>
-    <t xml:space="preserve">This ontology partially describes the built-in classes and  properties that together form the basis of the RDF/Turtle syntax of OWL 2.  The content of this ontology is based on Tables 6.1 and 6.2  in Section 6.4 of the OWL 2 RDF-Based Semantics specification,  available at http://www.w3.org/TR/owl2-rdf-based-semantics/.  Please note that those tables do not include the different annotations  (labels, comments and rdfs:isDefinedBy links) used in this file.  Also note that the descriptions provided in this ontology do not  provide a complete and correct formal description of either the syntax  or the semantics of the introduced terms (please see the OWL 2  recommendations for the complete and normative specifications).  Furthermore, the information provided by this ontology may be  misleading if not used with care. This ontology SHOULD NOT be imported  into OWL ontologies. Importing this file into an OWL 2 DL ontology  will cause it to become an OWL 2 Full ontology and may have other,  unexpected, consequences.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.w3.org/2002/07/owl#</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.w3.org/TR/owl2-overview/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OWL 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The OWL 2 Schema vocabulary (OWL 2)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20091115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Class URI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://xmlns.com/foaf/0.1/Agent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dct:spatial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dct:type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W3C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">foaf:Agent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://danbri.org/foaf.rdf#danbri</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dan Brickley</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://publications.europa.eu/resource/authority/country/GBR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://data.semanticweb.org/person/libby-miller</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Libby Miller</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DCMI Usage Board</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://publications.europa.eu/resource/authority/country/IRL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://www.w3.org/2000/01/rdf-schema#Class</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://inspire.ec.europa.eu/ont/ad#</t>
-  </si>
-  <si>
-    <t xml:space="preserve">legal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://www.w3.org/ns/legal#</t>
-  </si>
-  <si>
-    <t xml:space="preserve">locn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://www.w3.org/ns/locn#</t>
-  </si>
-  <si>
-    <t xml:space="preserve">person</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://www.w3.org/ns/person#</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rdfs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://www.w3.org/2000/01/rdf-schema#</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rdfs:label@en</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rdfs:isDefinedBy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dcat:Catalog</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Catalogue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rdfs:Class</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dcat:CatalogedResource</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Catalogued Resource</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dcat:CatalogRecord</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Catalog Record</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dcat:Dataset</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dataset</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dcat:DataService</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Service</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dcat:DatasetSeries</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dataset Series</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dcat:Distribution</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Distribution</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dcat:Relationship</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Relationship</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dcat:Resource</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Resource</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dcat:Role</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Role</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Agent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">foaf:Person</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Person</t>
-  </si>
-  <si>
-    <t xml:space="preserve">foaf:Project</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Project</t>
-  </si>
-  <si>
-    <t xml:space="preserve">foaf:Organization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Organization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">foaf:Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">foaf:Document</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Document</t>
-  </si>
-  <si>
-    <t xml:space="preserve">foaf:Image</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Image</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dct:Agent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dct:AgentClass</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Agent Class</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dct:BibliographicResource</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bibliographic Resource</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dct:FileFormat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">File Format</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dct:Frequency</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Frequency</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dct:Jurisdiction</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jurisdiction</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dct:LicenseDocument</t>
-  </si>
-  <si>
-    <t xml:space="preserve">License Document</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dct:LinguisticSystem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linguistic System</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dct:Location</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Location</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dct:LocationPeriodOrJurisdiction</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Location Period Or Jurisdiction</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dct:MediaType</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Media Type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dct:MediaTypeOrExtent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Media Type Or Extent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dct:MethodOfAccrual</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Method Of Accrual</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dct:MethodOfInstruction</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Method Of Instruction</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dct:PeriodOfTime</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Period Of Time</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dct:PhysicalMedium</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Physical Medium</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dct:PhysicalResource</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Physical Resource</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dct:Policy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Policy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dct:ProvenanceStatement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Provenance Statement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dct:RightsStatement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rights Statement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dct:SizeOrDuration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Size Or Duration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dct:Standard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Standard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">org:Organization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">org:FormalOrganization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Formal Organization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">org:OrganizationalUnit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Organizational Unit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">org:Membership</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Membership</t>
-  </si>
-  <si>
-    <t xml:space="preserve">org:Role</t>
-  </si>
-  <si>
-    <t xml:space="preserve">org:Post</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Post</t>
-  </si>
-  <si>
-    <t xml:space="preserve">org:Site</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site</t>
-  </si>
-  <si>
-    <t xml:space="preserve">org:OrganizationalCollaboration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Organizational Collaboration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">org:ChangeEvent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Change Event</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vcard:Acquaintance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Acquaintance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vcard:Address</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Address</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vcard:Agent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vcard:BBS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BBS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vcard:Car</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Car</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vcard:Cell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vcard:Child</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Child</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vcard:Colleague</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Colleague</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vcard:Contact</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Contact</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vcard:Correspondent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Correspondent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vcard:Coworker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coworker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vcard:Crush</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Crush</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vcard:Date</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Date</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vcard:Dom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vcard:Email</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Email</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vcard:Enemy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Enemy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vcard:Fax</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fax</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vcard:Female</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Female</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vcard:Friend</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Friend</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vcard:Gender</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gender</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vcard:Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vcard:Home</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Home</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vcard:Individual</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Individual</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vcard:Internet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Internet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vcard:Intl</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Intl</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vcard:ISDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ISDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vcard:Kin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vcard:Kind</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kind</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vcard:Label</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Label</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vcard:Location</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vcard:Male</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Male</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vcard:Me</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Me</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vcard:Met</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Met</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vcard:Modem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Modem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vcard:Msg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Msg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vcard:Muse</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Muse</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vcard:Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vcard:Neighbor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Neighbor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vcard:None</t>
-  </si>
-  <si>
-    <t xml:space="preserve">None</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vcard:Organization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vcard:Other</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Other</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vcard:Pager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vcard:Parcel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parcel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vcard:Parent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vcard:PCS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PCS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vcard:Phone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vcard:Postal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Postal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vcard:Pref</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pref</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vcard:RelationType</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Relation Type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vcard:Sibling</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sibling</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vcard:Spouse</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spouse</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vcard:Sweetheart</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sweetheart</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vcard:Tel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vcard:Text</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Text</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vcard:Textphone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Textphone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vcard:Type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vcard:Unknown</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unknown</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vcard:VCard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VCard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vcard:Video</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Video</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vcard:Voice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Voice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vcard:Work</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Work</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vcard:X400</t>
-  </si>
-  <si>
-    <t xml:space="preserve">X400</t>
-  </si>
-  <si>
-    <t xml:space="preserve">skos:Concept</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Concept</t>
-  </si>
-  <si>
-    <t xml:space="preserve">skos:ConceptScheme</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Concept Scheme</t>
-  </si>
-  <si>
-    <t xml:space="preserve">skos:Collection</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Collection</t>
-  </si>
-  <si>
-    <t xml:space="preserve">skos:OrderedCollection</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ordered Collection</t>
-  </si>
-  <si>
-    <t xml:space="preserve">owl:AllDifferent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">All Different</t>
-  </si>
-  <si>
-    <t xml:space="preserve">owl:AllDisjointClasses</t>
-  </si>
-  <si>
-    <t xml:space="preserve">All Disjoint Classes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">owl:AllDisjointProperties</t>
-  </si>
-  <si>
-    <t xml:space="preserve">All Disjoint Properties</t>
-  </si>
-  <si>
-    <t xml:space="preserve">owl:Annotation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Annotation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">owl:AnnotationProperty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Annotation Property</t>
-  </si>
-  <si>
-    <t xml:space="preserve">owl:AsymmetricProperty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Asymmetric Property</t>
-  </si>
-  <si>
-    <t xml:space="preserve">owl:Axiom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Axiom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">owl:Class</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Class</t>
-  </si>
-  <si>
-    <t xml:space="preserve">owl:DataRange</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Range</t>
-  </si>
-  <si>
-    <t xml:space="preserve">owl:DatatypeProperty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Datatype Property</t>
-  </si>
-  <si>
-    <t xml:space="preserve">owl:DeprecatedClass</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Deprecated Class</t>
-  </si>
-  <si>
-    <t xml:space="preserve">owl:DeprecatedProperty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Deprecated Property</t>
-  </si>
-  <si>
-    <t xml:space="preserve">owl:FunctionalProperty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Functional Property</t>
-  </si>
-  <si>
-    <t xml:space="preserve">owl:InverseFunctionalProperty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Inverse Functional Property</t>
-  </si>
-  <si>
-    <t xml:space="preserve">owl:IrreflexiveProperty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Irreflexive Property</t>
-  </si>
-  <si>
-    <t xml:space="preserve">owl:NamedIndividual</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Named Individual</t>
-  </si>
-  <si>
-    <t xml:space="preserve">owl:NegativePropertyAssertion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Negative Property Assertion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">owl:Nothing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nothing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">owl:ObjectProperty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Object Property</t>
-  </si>
-  <si>
-    <t xml:space="preserve">owl:Ontology</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ontology</t>
-  </si>
-  <si>
-    <t xml:space="preserve">owl:OntologyProperty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ontology Property</t>
-  </si>
-  <si>
-    <t xml:space="preserve">owl:ReflexiveProperty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reflexive Property</t>
-  </si>
-  <si>
-    <t xml:space="preserve">owl:Restriction</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Restriction</t>
-  </si>
-  <si>
-    <t xml:space="preserve">owl:SymmetricProperty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Symmetric Property</t>
-  </si>
-  <si>
-    <t xml:space="preserve">owl:TransitiveProperty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transitive Property</t>
-  </si>
-  <si>
-    <t xml:space="preserve">owl:Thing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://data.europa.eu/m8g/ContactPoint</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cv:hasMail^^xsd:string</t>
-  </si>
-  <si>
-    <t xml:space="preserve">contact@w3.org</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cv:ContactPoint</t>
-  </si>
-  <si>
-    <t xml:space="preserve">danbri@danbri.org</t>
-  </si>
-  <si>
-    <t xml:space="preserve">libby@nicecupoftea.org</t>
-  </si>
-  <si>
-    <t xml:space="preserve">contact@dublincore.net</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://xmlns.com/foaf/0.1/Document</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://purl.org/dc/terms/Location</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://www.w3.org/ns/adms#AssetDistribution</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dcat:downloadURL^^xsd:anyURI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dct:format</t>
-  </si>
-  <si>
-    <t xml:space="preserve">prof:hasRole</t>
-  </si>
-  <si>
-    <t xml:space="preserve">adms:AssetDistribution</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://publications.europa.eu/resource/authority/file-type/RDF_TURTLE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://www.w3.org/ns/dx/prof/role/vocabulary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RDF Turtle file of DCAT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RDF Turtle file of FOAF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RDF Turtle file of DC Terms</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RDF Turtle file of W3C Organization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RDF Turtle file of W3C vCard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RDF Turtle file of W3C OWL 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RDF Turtle file of W3C SKOS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://www.w3.org/2004/02/skos/core#Concept</t>
-  </si>
-  <si>
-    <t xml:space="preserve">skos:inScheme</t>
-  </si>
-  <si>
-    <t xml:space="preserve">skos:topConceptOf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://publications.europa.eu/resource/authority/file-type/RDF</t>
+    <t>3.0.0</t>
+  </si>
+  <si>
+    <t>adms:Asset</t>
+  </si>
+  <si>
+    <t>https://danbri.org/foaf.rdf#danbri,http://data.semanticweb.org/person/libby-miller</t>
+  </si>
+  <si>
+    <t>FOAF is a project devoted to linking people and information using the Web. Regardless of whether information is in people's heads, in physical or digital documents, or in the form of factual data, it can be linked. FOAF integrates three kinds of network: social networks of human collaboration, friendship and association; representational networks that describe a simplified view of a cartoon universe in factual terms, and information networks that use Web-based linking to share independently published descriptions of this inter-connected world. FOAF does not compete with socially-oriented Web sites; rather it provides an approach in which different sites can tell different parts of the larger story, and by which users can retain some control over their information in a non-proprietary format.</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/SEMICeu/EU-wide-Registry-of-Semantic-Models/refs/heads/main/SR-dev/foaf.ttl</t>
+  </si>
+  <si>
+    <t>http://xmlns.com/foaf/spec/</t>
+  </si>
+  <si>
+    <t>FOAF</t>
+  </si>
+  <si>
+    <t>Friend of a Friend (FOAF) vocabulary</t>
+  </si>
+  <si>
+    <t>0.99</t>
+  </si>
+  <si>
+    <t>http://purl.org/dc/aboutdcmi#DCMI</t>
+  </si>
+  <si>
+    <t>This document is an up-to-date specification of all metadata terms maintained by the Dublin Core Metadata Initiative, including properties, vocabulary encoding schemes, syntax encoding schemes, and classes.</t>
+  </si>
+  <si>
+    <t>https://www.dublincore.org/specifications/dublin-core/dcmi-terms/dublin_core_terms.ttl</t>
+  </si>
+  <si>
+    <t>https://www.dublincore.org/specifications/dublin-core/dcmi-terms/</t>
+  </si>
+  <si>
+    <t>DC Terms</t>
+  </si>
+  <si>
+    <t>DCMI Metadata Terms - other</t>
+  </si>
+  <si>
+    <t>2020-01-20</t>
+  </si>
+  <si>
+    <t>Vocabulary for describing organizational structures, specializable to a broad variety of types of organization.</t>
+  </si>
+  <si>
+    <t>https://www.w3.org/ns/org.ttl</t>
+  </si>
+  <si>
+    <t>https://www.w3.org/TR/vocab-org/</t>
+  </si>
+  <si>
+    <t>W3C Org</t>
+  </si>
+  <si>
+    <t>Core organization ontology</t>
+  </si>
+  <si>
+    <t>0.08</t>
+  </si>
+  <si>
+    <t>Ontology for vCard based on RFC6350</t>
+  </si>
+  <si>
+    <t>https://www.w3.org/2006/vcard/ns#</t>
+  </si>
+  <si>
+    <t>https://www.w3.org/TR/vcard-rdf/#Ontology</t>
+  </si>
+  <si>
+    <t>W3C vCard</t>
+  </si>
+  <si>
+    <t>Ontology for vCard</t>
+  </si>
+  <si>
+    <t>Final</t>
+  </si>
+  <si>
+    <t>http://www.w3.org/2004/02/skos/core</t>
+  </si>
+  <si>
+    <t>An RDF vocabulary for describing the basic structure and content of concept schemes such as thesauri, classification schemes, subject heading lists, taxonomies, 'folksonomies', other types of controlled vocabulary, and also concept schemes embedded in glossaries and terminologies.</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/SEMICeu/EU-wide-Registry-of-Semantic-Models/refs/heads/main/SR-dev/skos.ttl</t>
+  </si>
+  <si>
+    <t>https://www.w3.org/TR/skos-reference/</t>
+  </si>
+  <si>
+    <t>SKOS</t>
+  </si>
+  <si>
+    <t>SKOS Vocabulary</t>
+  </si>
+  <si>
+    <t>20090818</t>
+  </si>
+  <si>
+    <t>http://www.w3.org/2002/07/owl</t>
+  </si>
+  <si>
+    <t>This ontology partially describes the built-in classes and  properties that together form the basis of the RDF/Turtle syntax of OWL 2.  The content of this ontology is based on Tables 6.1 and 6.2  in Section 6.4 of the OWL 2 RDF-Based Semantics specification,  available at http://www.w3.org/TR/owl2-rdf-based-semantics/.  Please note that those tables do not include the different annotations  (labels, comments and rdfs:isDefinedBy links) used in this file.  Also note that the descriptions provided in this ontology do not  provide a complete and correct formal description of either the syntax  or the semantics of the introduced terms (please see the OWL 2  recommendations for the complete and normative specifications).  Furthermore, the information provided by this ontology may be  misleading if not used with care. This ontology SHOULD NOT be imported  into OWL ontologies. Importing this file into an OWL 2 DL ontology  will cause it to become an OWL 2 Full ontology and may have other,  unexpected, consequences.</t>
+  </si>
+  <si>
+    <t>https://www.w3.org/2002/07/owl#</t>
+  </si>
+  <si>
+    <t>https://www.w3.org/TR/owl2-overview/</t>
+  </si>
+  <si>
+    <t>OWL 2</t>
+  </si>
+  <si>
+    <t>The OWL 2 Schema vocabulary (OWL 2)</t>
+  </si>
+  <si>
+    <t>20091115</t>
+  </si>
+  <si>
+    <t>Class URI</t>
+  </si>
+  <si>
+    <t>http://xmlns.com/foaf/0.1/Agent</t>
+  </si>
+  <si>
+    <t>dct:spatial</t>
+  </si>
+  <si>
+    <t>dct:type</t>
+  </si>
+  <si>
+    <t>W3C</t>
+  </si>
+  <si>
+    <t>foaf:Agent</t>
+  </si>
+  <si>
+    <t>https://danbri.org/foaf.rdf#danbri</t>
+  </si>
+  <si>
+    <t>Dan Brickley</t>
+  </si>
+  <si>
+    <t>http://publications.europa.eu/resource/authority/country/GBR</t>
+  </si>
+  <si>
+    <t>http://data.semanticweb.org/person/libby-miller</t>
+  </si>
+  <si>
+    <t>Libby Miller</t>
+  </si>
+  <si>
+    <t>DCMI Usage Board</t>
+  </si>
+  <si>
+    <t>http://publications.europa.eu/resource/authority/country/IRL</t>
+  </si>
+  <si>
+    <t>http://www.w3.org/2000/01/rdf-schema#Class</t>
+  </si>
+  <si>
+    <t>ad</t>
+  </si>
+  <si>
+    <t>http://inspire.ec.europa.eu/ont/ad#</t>
+  </si>
+  <si>
+    <t>legal</t>
+  </si>
+  <si>
+    <t>http://www.w3.org/ns/legal#</t>
+  </si>
+  <si>
+    <t>locn</t>
+  </si>
+  <si>
+    <t>http://www.w3.org/ns/locn#</t>
+  </si>
+  <si>
+    <t>person</t>
+  </si>
+  <si>
+    <t>http://www.w3.org/ns/person#</t>
+  </si>
+  <si>
+    <t>rdfs</t>
+  </si>
+  <si>
+    <t>http://www.w3.org/2000/01/rdf-schema#</t>
+  </si>
+  <si>
+    <t>rdfs:label@en</t>
+  </si>
+  <si>
+    <t>rdfs:isDefinedBy</t>
+  </si>
+  <si>
+    <t>dcat:Catalog</t>
+  </si>
+  <si>
+    <t>Catalogue</t>
+  </si>
+  <si>
+    <t>rdfs:Class</t>
+  </si>
+  <si>
+    <t>dcat:CatalogedResource</t>
+  </si>
+  <si>
+    <t>Catalogued Resource</t>
+  </si>
+  <si>
+    <t>dcat:CatalogRecord</t>
+  </si>
+  <si>
+    <t>Catalog Record</t>
+  </si>
+  <si>
+    <t>dcat:Dataset</t>
+  </si>
+  <si>
+    <t>Dataset</t>
+  </si>
+  <si>
+    <t>dcat:DataService</t>
+  </si>
+  <si>
+    <t>Data Service</t>
+  </si>
+  <si>
+    <t>dcat:DatasetSeries</t>
+  </si>
+  <si>
+    <t>Dataset Series</t>
+  </si>
+  <si>
+    <t>dcat:Distribution</t>
+  </si>
+  <si>
+    <t>Distribution</t>
+  </si>
+  <si>
+    <t>dcat:Relationship</t>
+  </si>
+  <si>
+    <t>Relationship</t>
+  </si>
+  <si>
+    <t>dcat:Resource</t>
+  </si>
+  <si>
+    <t>Resource</t>
+  </si>
+  <si>
+    <t>dcat:Role</t>
+  </si>
+  <si>
+    <t>Role</t>
+  </si>
+  <si>
+    <t>Agent</t>
+  </si>
+  <si>
+    <t>foaf:Person</t>
+  </si>
+  <si>
+    <t>Person</t>
+  </si>
+  <si>
+    <t>foaf:Project</t>
+  </si>
+  <si>
+    <t>Project</t>
+  </si>
+  <si>
+    <t>foaf:Organization</t>
+  </si>
+  <si>
+    <t>Organization</t>
+  </si>
+  <si>
+    <t>foaf:Group</t>
+  </si>
+  <si>
+    <t>Group</t>
+  </si>
+  <si>
+    <t>foaf:Document</t>
+  </si>
+  <si>
+    <t>Document</t>
+  </si>
+  <si>
+    <t>foaf:Image</t>
+  </si>
+  <si>
+    <t>Image</t>
+  </si>
+  <si>
+    <t>dct:Agent</t>
+  </si>
+  <si>
+    <t>dct:AgentClass</t>
+  </si>
+  <si>
+    <t>Agent Class</t>
+  </si>
+  <si>
+    <t>dct:BibliographicResource</t>
+  </si>
+  <si>
+    <t>Bibliographic Resource</t>
+  </si>
+  <si>
+    <t>dct:FileFormat</t>
+  </si>
+  <si>
+    <t>File Format</t>
+  </si>
+  <si>
+    <t>dct:Frequency</t>
+  </si>
+  <si>
+    <t>Frequency</t>
+  </si>
+  <si>
+    <t>dct:Jurisdiction</t>
+  </si>
+  <si>
+    <t>Jurisdiction</t>
+  </si>
+  <si>
+    <t>dct:LicenseDocument</t>
+  </si>
+  <si>
+    <t>License Document</t>
+  </si>
+  <si>
+    <t>dct:LinguisticSystem</t>
+  </si>
+  <si>
+    <t>Linguistic System</t>
+  </si>
+  <si>
+    <t>dct:Location</t>
+  </si>
+  <si>
+    <t>Location</t>
+  </si>
+  <si>
+    <t>dct:LocationPeriodOrJurisdiction</t>
+  </si>
+  <si>
+    <t>Location Period Or Jurisdiction</t>
+  </si>
+  <si>
+    <t>dct:MediaType</t>
+  </si>
+  <si>
+    <t>Media Type</t>
+  </si>
+  <si>
+    <t>dct:MediaTypeOrExtent</t>
+  </si>
+  <si>
+    <t>Media Type Or Extent</t>
+  </si>
+  <si>
+    <t>dct:MethodOfAccrual</t>
+  </si>
+  <si>
+    <t>Method Of Accrual</t>
+  </si>
+  <si>
+    <t>dct:MethodOfInstruction</t>
+  </si>
+  <si>
+    <t>Method Of Instruction</t>
+  </si>
+  <si>
+    <t>dct:PeriodOfTime</t>
+  </si>
+  <si>
+    <t>Period Of Time</t>
+  </si>
+  <si>
+    <t>dct:PhysicalMedium</t>
+  </si>
+  <si>
+    <t>Physical Medium</t>
+  </si>
+  <si>
+    <t>dct:PhysicalResource</t>
+  </si>
+  <si>
+    <t>Physical Resource</t>
+  </si>
+  <si>
+    <t>dct:Policy</t>
+  </si>
+  <si>
+    <t>Policy</t>
+  </si>
+  <si>
+    <t>dct:ProvenanceStatement</t>
+  </si>
+  <si>
+    <t>Provenance Statement</t>
+  </si>
+  <si>
+    <t>dct:RightsStatement</t>
+  </si>
+  <si>
+    <t>Rights Statement</t>
+  </si>
+  <si>
+    <t>dct:SizeOrDuration</t>
+  </si>
+  <si>
+    <t>Size Or Duration</t>
+  </si>
+  <si>
+    <t>dct:Standard</t>
+  </si>
+  <si>
+    <t>Standard</t>
+  </si>
+  <si>
+    <t>org:Organization</t>
+  </si>
+  <si>
+    <t>org:FormalOrganization</t>
+  </si>
+  <si>
+    <t>Formal Organization</t>
+  </si>
+  <si>
+    <t>org:OrganizationalUnit</t>
+  </si>
+  <si>
+    <t>Organizational Unit</t>
+  </si>
+  <si>
+    <t>org:Membership</t>
+  </si>
+  <si>
+    <t>Membership</t>
+  </si>
+  <si>
+    <t>org:Role</t>
+  </si>
+  <si>
+    <t>org:Post</t>
+  </si>
+  <si>
+    <t>Post</t>
+  </si>
+  <si>
+    <t>org:Site</t>
+  </si>
+  <si>
+    <t>Site</t>
+  </si>
+  <si>
+    <t>org:OrganizationalCollaboration</t>
+  </si>
+  <si>
+    <t>Organizational Collaboration</t>
+  </si>
+  <si>
+    <t>org:ChangeEvent</t>
+  </si>
+  <si>
+    <t>Change Event</t>
+  </si>
+  <si>
+    <t>vcard:Acquaintance</t>
+  </si>
+  <si>
+    <t>Acquaintance</t>
+  </si>
+  <si>
+    <t>vcard:Address</t>
+  </si>
+  <si>
+    <t>Address</t>
+  </si>
+  <si>
+    <t>vcard:Agent</t>
+  </si>
+  <si>
+    <t>vcard:BBS</t>
+  </si>
+  <si>
+    <t>BBS</t>
+  </si>
+  <si>
+    <t>vcard:Car</t>
+  </si>
+  <si>
+    <t>Car</t>
+  </si>
+  <si>
+    <t>vcard:Cell</t>
+  </si>
+  <si>
+    <t>Cell</t>
+  </si>
+  <si>
+    <t>vcard:Child</t>
+  </si>
+  <si>
+    <t>Child</t>
+  </si>
+  <si>
+    <t>vcard:Colleague</t>
+  </si>
+  <si>
+    <t>Colleague</t>
+  </si>
+  <si>
+    <t>vcard:Contact</t>
+  </si>
+  <si>
+    <t>Contact</t>
+  </si>
+  <si>
+    <t>vcard:Correspondent</t>
+  </si>
+  <si>
+    <t>Correspondent</t>
+  </si>
+  <si>
+    <t>vcard:Coworker</t>
+  </si>
+  <si>
+    <t>Coworker</t>
+  </si>
+  <si>
+    <t>vcard:Crush</t>
+  </si>
+  <si>
+    <t>Crush</t>
+  </si>
+  <si>
+    <t>vcard:Date</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>vcard:Dom</t>
+  </si>
+  <si>
+    <t>Dom</t>
+  </si>
+  <si>
+    <t>vcard:Email</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>vcard:Enemy</t>
+  </si>
+  <si>
+    <t>Enemy</t>
+  </si>
+  <si>
+    <t>vcard:Fax</t>
+  </si>
+  <si>
+    <t>Fax</t>
+  </si>
+  <si>
+    <t>vcard:Female</t>
+  </si>
+  <si>
+    <t>Female</t>
+  </si>
+  <si>
+    <t>vcard:Friend</t>
+  </si>
+  <si>
+    <t>Friend</t>
+  </si>
+  <si>
+    <t>vcard:Gender</t>
+  </si>
+  <si>
+    <t>Gender</t>
+  </si>
+  <si>
+    <t>vcard:Group</t>
+  </si>
+  <si>
+    <t>vcard:Home</t>
+  </si>
+  <si>
+    <t>Home</t>
+  </si>
+  <si>
+    <t>vcard:Individual</t>
+  </si>
+  <si>
+    <t>Individual</t>
+  </si>
+  <si>
+    <t>vcard:Internet</t>
+  </si>
+  <si>
+    <t>Internet</t>
+  </si>
+  <si>
+    <t>vcard:Intl</t>
+  </si>
+  <si>
+    <t>Intl</t>
+  </si>
+  <si>
+    <t>vcard:ISDN</t>
+  </si>
+  <si>
+    <t>ISDN</t>
+  </si>
+  <si>
+    <t>vcard:Kin</t>
+  </si>
+  <si>
+    <t>Kin</t>
+  </si>
+  <si>
+    <t>vcard:Kind</t>
+  </si>
+  <si>
+    <t>Kind</t>
+  </si>
+  <si>
+    <t>vcard:Label</t>
+  </si>
+  <si>
+    <t>Label</t>
+  </si>
+  <si>
+    <t>vcard:Location</t>
+  </si>
+  <si>
+    <t>vcard:Male</t>
+  </si>
+  <si>
+    <t>Male</t>
+  </si>
+  <si>
+    <t>vcard:Me</t>
+  </si>
+  <si>
+    <t>Me</t>
+  </si>
+  <si>
+    <t>vcard:Met</t>
+  </si>
+  <si>
+    <t>Met</t>
+  </si>
+  <si>
+    <t>vcard:Modem</t>
+  </si>
+  <si>
+    <t>Modem</t>
+  </si>
+  <si>
+    <t>vcard:Msg</t>
+  </si>
+  <si>
+    <t>Msg</t>
+  </si>
+  <si>
+    <t>vcard:Muse</t>
+  </si>
+  <si>
+    <t>Muse</t>
+  </si>
+  <si>
+    <t>vcard:Name</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>vcard:Neighbor</t>
+  </si>
+  <si>
+    <t>Neighbor</t>
+  </si>
+  <si>
+    <t>vcard:None</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>vcard:Organization</t>
+  </si>
+  <si>
+    <t>vcard:Other</t>
+  </si>
+  <si>
+    <t>Other</t>
+  </si>
+  <si>
+    <t>vcard:Pager</t>
+  </si>
+  <si>
+    <t>Pager</t>
+  </si>
+  <si>
+    <t>vcard:Parcel</t>
+  </si>
+  <si>
+    <t>Parcel</t>
+  </si>
+  <si>
+    <t>vcard:Parent</t>
+  </si>
+  <si>
+    <t>Parent</t>
+  </si>
+  <si>
+    <t>vcard:PCS</t>
+  </si>
+  <si>
+    <t>PCS</t>
+  </si>
+  <si>
+    <t>vcard:Phone</t>
+  </si>
+  <si>
+    <t>Phone</t>
+  </si>
+  <si>
+    <t>vcard:Postal</t>
+  </si>
+  <si>
+    <t>Postal</t>
+  </si>
+  <si>
+    <t>vcard:Pref</t>
+  </si>
+  <si>
+    <t>Pref</t>
+  </si>
+  <si>
+    <t>vcard:RelationType</t>
+  </si>
+  <si>
+    <t>Relation Type</t>
+  </si>
+  <si>
+    <t>vcard:Sibling</t>
+  </si>
+  <si>
+    <t>Sibling</t>
+  </si>
+  <si>
+    <t>vcard:Spouse</t>
+  </si>
+  <si>
+    <t>Spouse</t>
+  </si>
+  <si>
+    <t>vcard:Sweetheart</t>
+  </si>
+  <si>
+    <t>Sweetheart</t>
+  </si>
+  <si>
+    <t>vcard:Tel</t>
+  </si>
+  <si>
+    <t>Tel</t>
+  </si>
+  <si>
+    <t>vcard:Text</t>
+  </si>
+  <si>
+    <t>Text</t>
+  </si>
+  <si>
+    <t>vcard:Textphone</t>
+  </si>
+  <si>
+    <t>Textphone</t>
+  </si>
+  <si>
+    <t>vcard:Type</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>vcard:Unknown</t>
+  </si>
+  <si>
+    <t>Unknown</t>
+  </si>
+  <si>
+    <t>vcard:VCard</t>
+  </si>
+  <si>
+    <t>VCard</t>
+  </si>
+  <si>
+    <t>vcard:Video</t>
+  </si>
+  <si>
+    <t>Video</t>
+  </si>
+  <si>
+    <t>vcard:Voice</t>
+  </si>
+  <si>
+    <t>Voice</t>
+  </si>
+  <si>
+    <t>vcard:Work</t>
+  </si>
+  <si>
+    <t>Work</t>
+  </si>
+  <si>
+    <t>vcard:X400</t>
+  </si>
+  <si>
+    <t>X400</t>
+  </si>
+  <si>
+    <t>skos:Concept</t>
+  </si>
+  <si>
+    <t>Concept</t>
+  </si>
+  <si>
+    <t>skos:ConceptScheme</t>
+  </si>
+  <si>
+    <t>Concept Scheme</t>
+  </si>
+  <si>
+    <t>skos:Collection</t>
+  </si>
+  <si>
+    <t>Collection</t>
+  </si>
+  <si>
+    <t>skos:OrderedCollection</t>
+  </si>
+  <si>
+    <t>Ordered Collection</t>
+  </si>
+  <si>
+    <t>owl:AllDifferent</t>
+  </si>
+  <si>
+    <t>All Different</t>
+  </si>
+  <si>
+    <t>owl:AllDisjointClasses</t>
+  </si>
+  <si>
+    <t>All Disjoint Classes</t>
+  </si>
+  <si>
+    <t>owl:AllDisjointProperties</t>
+  </si>
+  <si>
+    <t>All Disjoint Properties</t>
+  </si>
+  <si>
+    <t>owl:Annotation</t>
+  </si>
+  <si>
+    <t>Annotation</t>
+  </si>
+  <si>
+    <t>owl:AnnotationProperty</t>
+  </si>
+  <si>
+    <t>Annotation Property</t>
+  </si>
+  <si>
+    <t>owl:AsymmetricProperty</t>
+  </si>
+  <si>
+    <t>Asymmetric Property</t>
+  </si>
+  <si>
+    <t>owl:Axiom</t>
+  </si>
+  <si>
+    <t>Axiom</t>
+  </si>
+  <si>
+    <t>owl:Class</t>
+  </si>
+  <si>
+    <t>Class</t>
+  </si>
+  <si>
+    <t>owl:DataRange</t>
+  </si>
+  <si>
+    <t>Data Range</t>
+  </si>
+  <si>
+    <t>owl:DatatypeProperty</t>
+  </si>
+  <si>
+    <t>Datatype Property</t>
+  </si>
+  <si>
+    <t>owl:DeprecatedClass</t>
+  </si>
+  <si>
+    <t>Deprecated Class</t>
+  </si>
+  <si>
+    <t>owl:DeprecatedProperty</t>
+  </si>
+  <si>
+    <t>Deprecated Property</t>
+  </si>
+  <si>
+    <t>owl:FunctionalProperty</t>
+  </si>
+  <si>
+    <t>Functional Property</t>
+  </si>
+  <si>
+    <t>owl:InverseFunctionalProperty</t>
+  </si>
+  <si>
+    <t>Inverse Functional Property</t>
+  </si>
+  <si>
+    <t>owl:IrreflexiveProperty</t>
+  </si>
+  <si>
+    <t>Irreflexive Property</t>
+  </si>
+  <si>
+    <t>owl:NamedIndividual</t>
+  </si>
+  <si>
+    <t>Named Individual</t>
+  </si>
+  <si>
+    <t>owl:NegativePropertyAssertion</t>
+  </si>
+  <si>
+    <t>Negative Property Assertion</t>
+  </si>
+  <si>
+    <t>owl:Nothing</t>
+  </si>
+  <si>
+    <t>Nothing</t>
+  </si>
+  <si>
+    <t>owl:ObjectProperty</t>
+  </si>
+  <si>
+    <t>Object Property</t>
+  </si>
+  <si>
+    <t>owl:Ontology</t>
+  </si>
+  <si>
+    <t>Ontology</t>
+  </si>
+  <si>
+    <t>owl:OntologyProperty</t>
+  </si>
+  <si>
+    <t>Ontology Property</t>
+  </si>
+  <si>
+    <t>owl:ReflexiveProperty</t>
+  </si>
+  <si>
+    <t>Reflexive Property</t>
+  </si>
+  <si>
+    <t>owl:Restriction</t>
+  </si>
+  <si>
+    <t>Restriction</t>
+  </si>
+  <si>
+    <t>owl:SymmetricProperty</t>
+  </si>
+  <si>
+    <t>Symmetric Property</t>
+  </si>
+  <si>
+    <t>owl:TransitiveProperty</t>
+  </si>
+  <si>
+    <t>Transitive Property</t>
+  </si>
+  <si>
+    <t>owl:Thing</t>
+  </si>
+  <si>
+    <t>Thing</t>
+  </si>
+  <si>
+    <t>http://data.europa.eu/m8g/ContactPoint</t>
+  </si>
+  <si>
+    <t>cv:hasMail^^xsd:string</t>
+  </si>
+  <si>
+    <t>contact@w3.org</t>
+  </si>
+  <si>
+    <t>cv:ContactPoint</t>
+  </si>
+  <si>
+    <t>danbri@danbri.org</t>
+  </si>
+  <si>
+    <t>libby@nicecupoftea.org</t>
+  </si>
+  <si>
+    <t>contact@dublincore.net</t>
+  </si>
+  <si>
+    <t>http://xmlns.com/foaf/0.1/Document</t>
+  </si>
+  <si>
+    <t>http://purl.org/dc/terms/Location</t>
+  </si>
+  <si>
+    <t>http://www.w3.org/ns/adms#AssetDistribution</t>
+  </si>
+  <si>
+    <t>dcat:downloadURL^^xsd:anyURI</t>
+  </si>
+  <si>
+    <t>dct:format</t>
+  </si>
+  <si>
+    <t>prof:hasRole</t>
+  </si>
+  <si>
+    <t>adms:AssetDistribution</t>
+  </si>
+  <si>
+    <t>http://publications.europa.eu/resource/authority/file-type/RDF_TURTLE</t>
+  </si>
+  <si>
+    <t>http://www.w3.org/ns/dx/prof/role/vocabulary</t>
+  </si>
+  <si>
+    <t>RDF Turtle file of DCAT</t>
+  </si>
+  <si>
+    <t>RDF Turtle file of FOAF</t>
+  </si>
+  <si>
+    <t>RDF Turtle file of DC Terms</t>
+  </si>
+  <si>
+    <t>RDF Turtle file of W3C Organization</t>
+  </si>
+  <si>
+    <t>RDF Turtle file of W3C vCard</t>
+  </si>
+  <si>
+    <t>RDF Turtle file of W3C OWL 2</t>
+  </si>
+  <si>
+    <t>RDF Turtle file of W3C SKOS</t>
+  </si>
+  <si>
+    <t>http://www.w3.org/2004/02/skos/core#Concept</t>
+  </si>
+  <si>
+    <t>skos:inScheme</t>
+  </si>
+  <si>
+    <t>skos:topConceptOf</t>
+  </si>
+  <si>
+    <t>http://publications.europa.eu/resource/authority/file-type/RDF</t>
+  </si>
+  <si>
+    <t>foaf:name@en</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="mm/dd/yyyy"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1361,40 +1343,20 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
       <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <u val="single"/>
+      <u/>
       <sz val="11"/>
       <color theme="10"/>
       <name val="Calibri"/>
@@ -1402,7 +1364,7 @@
       <charset val="1"/>
     </font>
     <font>
-      <u val="single"/>
+      <u/>
       <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -1424,13 +1386,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.7999"/>
+        <fgColor theme="6" tint="0.79989013336588644"/>
         <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
   </fills>
   <borders count="1">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
@@ -1438,97 +1400,44 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="21">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+  <cellStyleXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
+  </cellStyleXfs>
+  <cellXfs count="12">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-  </cellStyleXfs>
-  <cellXfs count="13">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="7">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
-    <cellStyle name="*unknown*" xfId="20" builtinId="8"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -1587,47 +1496,63 @@
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF333399"/>
       <rgbColor rgb="FF333333"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
     <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1f497d"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="eeece1"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4f81bd"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="c0504d"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9bbb59"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064a2"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4bacc6"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="f79646"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ff"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -1635,12 +1560,12 @@
     </a:clrScheme>
     <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -1669,7 +1594,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -1690,7 +1615,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -1741,7 +1666,7 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -1759,49 +1684,48 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:X26"/>
-  <sheetFormatPr defaultColWidth="11.5625" defaultRowHeight="14.25" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="50.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="32.34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="21.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="10.56"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="24.11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="9.44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="11.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="18.34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="20.11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="14.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="14.11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="23.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="12.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="12.56"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="58.56"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="9.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="27.34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="1" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="1" width="11.11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="1" width="10.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="1" width="20.56"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="1" width="14.33"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="24" style="1" width="11.56"/>
+    <col min="1" max="1" width="50.33203125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="32.33203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="21.33203125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="10.5546875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="24.109375" style="2" customWidth="1"/>
+    <col min="6" max="6" width="9.44140625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="11.6640625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="18.33203125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="20.109375" style="1" customWidth="1"/>
+    <col min="10" max="10" width="14.88671875" style="1" customWidth="1"/>
+    <col min="11" max="11" width="14.109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="23.6640625" style="1" customWidth="1"/>
+    <col min="13" max="13" width="12.88671875" style="1" customWidth="1"/>
+    <col min="14" max="14" width="12.5546875" style="1" customWidth="1"/>
+    <col min="15" max="15" width="58.5546875" style="1" customWidth="1"/>
+    <col min="16" max="16" width="9.6640625" style="1" customWidth="1"/>
+    <col min="17" max="17" width="27.33203125" style="1" customWidth="1"/>
+    <col min="18" max="18" width="12" style="1" customWidth="1"/>
+    <col min="19" max="19" width="11" style="1" customWidth="1"/>
+    <col min="20" max="20" width="11.109375" style="1" customWidth="1"/>
+    <col min="21" max="21" width="10.6640625" style="1" customWidth="1"/>
+    <col min="22" max="22" width="20.5546875" style="1" customWidth="1"/>
+    <col min="23" max="23" width="14.33203125" style="1" customWidth="1"/>
+    <col min="24" max="16384" width="11.5546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1809,7 +1733,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
@@ -1820,7 +1744,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -1831,7 +1755,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
@@ -1842,7 +1766,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>2</v>
       </c>
@@ -1853,7 +1777,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>2</v>
       </c>
@@ -1864,7 +1788,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>2</v>
       </c>
@@ -1875,7 +1799,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>2</v>
       </c>
@@ -1886,7 +1810,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>2</v>
       </c>
@@ -1897,7 +1821,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>2</v>
       </c>
@@ -1908,7 +1832,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>2</v>
       </c>
@@ -1919,7 +1843,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>2</v>
       </c>
@@ -1930,7 +1854,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>2</v>
       </c>
@@ -1941,7 +1865,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
         <v>2</v>
       </c>
@@ -1952,7 +1876,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
         <v>2</v>
       </c>
@@ -1963,7 +1887,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>2</v>
       </c>
@@ -1974,7 +1898,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" spans="1:24" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
         <v>2</v>
       </c>
@@ -1985,7 +1909,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" spans="1:24" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
         <v>31</v>
       </c>
@@ -2059,7 +1983,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" spans="1:24" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>10</v>
       </c>
@@ -2070,7 +1994,7 @@
       <c r="D20" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="E20" s="8" t="n">
+      <c r="E20" s="8">
         <v>44182</v>
       </c>
       <c r="H20" s="1" t="s">
@@ -2104,7 +2028,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="92.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" spans="1:24" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>14</v>
       </c>
@@ -2114,7 +2038,7 @@
       <c r="D21" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="E21" s="8" t="n">
+      <c r="E21" s="8">
         <v>41653</v>
       </c>
       <c r="H21" s="1" t="s">
@@ -2148,7 +2072,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="58.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" spans="1:24" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>12</v>
       </c>
@@ -2158,7 +2082,7 @@
       <c r="D22" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="E22" s="8" t="n">
+      <c r="E22" s="8">
         <v>41074</v>
       </c>
       <c r="H22" s="1" t="s">
@@ -2192,7 +2116,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" spans="1:24" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>26</v>
       </c>
@@ -2202,7 +2126,7 @@
       <c r="D23" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="E23" s="8" t="n">
+      <c r="E23" s="8">
         <v>41655</v>
       </c>
       <c r="H23" s="1" t="s">
@@ -2236,7 +2160,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" spans="1:24" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>28</v>
       </c>
@@ -2246,7 +2170,7 @@
       <c r="D24" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="E24" s="8" t="n">
+      <c r="E24" s="8">
         <v>41781</v>
       </c>
       <c r="H24" s="1" t="s">
@@ -2280,7 +2204,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" spans="1:24" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>90</v>
       </c>
@@ -2290,7 +2214,7 @@
       <c r="D25" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="E25" s="8" t="n">
+      <c r="E25" s="8">
         <v>40043</v>
       </c>
       <c r="H25" s="1" t="s">
@@ -2324,7 +2248,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" spans="1:24" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
         <v>97</v>
       </c>
@@ -2334,13 +2258,13 @@
       <c r="D26" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="E26" s="9" t="n">
+      <c r="E26" s="9">
         <v>41254</v>
       </c>
       <c r="H26" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="J26" s="10" t="s">
+      <c r="J26" s="1" t="s">
         <v>99</v>
       </c>
       <c r="K26" s="1" t="s">
@@ -2369,34 +2293,25 @@
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-  <legacyDrawing r:id="rId2"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E18"/>
-  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.25" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.5546875" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="41.56"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="28.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="61.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="13.34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="9.67"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="6" style="1" width="8.54"/>
+    <col min="1" max="1" width="41.5546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="28.6640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="61.6640625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="13.33203125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="9.6640625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="8.5546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>104</v>
       </c>
@@ -2405,7 +2320,7 @@
       </c>
       <c r="D1" s="2"/>
     </row>
-    <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
@@ -2417,7 +2332,7 @@
       </c>
       <c r="D2" s="2"/>
     </row>
-    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -2429,7 +2344,7 @@
       </c>
       <c r="D3" s="2"/>
     </row>
-    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
@@ -2441,7 +2356,7 @@
       </c>
       <c r="D4" s="2"/>
     </row>
-    <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>2</v>
       </c>
@@ -2453,7 +2368,7 @@
       </c>
       <c r="D5" s="2"/>
     </row>
-    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>2</v>
       </c>
@@ -2465,7 +2380,7 @@
       </c>
       <c r="D6" s="2"/>
     </row>
-    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>2</v>
       </c>
@@ -2477,7 +2392,7 @@
       </c>
       <c r="D7" s="2"/>
     </row>
-    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>2</v>
       </c>
@@ -2489,7 +2404,7 @@
       </c>
       <c r="D8" s="2"/>
     </row>
-    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>2</v>
       </c>
@@ -2501,7 +2416,7 @@
       </c>
       <c r="D9" s="2"/>
     </row>
-    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>2</v>
       </c>
@@ -2513,7 +2428,7 @@
       </c>
       <c r="D10" s="2"/>
     </row>
-    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>2</v>
       </c>
@@ -2525,7 +2440,7 @@
       </c>
       <c r="D11" s="2"/>
     </row>
-    <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>2</v>
       </c>
@@ -2537,15 +2452,15 @@
       </c>
       <c r="D12" s="2"/>
     </row>
-    <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D13" s="2"/>
     </row>
-    <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
         <v>31</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>52</v>
+        <v>430</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>106</v>
@@ -2557,7 +2472,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>55</v>
       </c>
@@ -2568,7 +2483,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>110</v>
       </c>
@@ -2582,7 +2497,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>113</v>
       </c>
@@ -2596,7 +2511,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>71</v>
       </c>
@@ -2611,32 +2526,24 @@
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:D159"/>
-  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.25" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.5546875" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="31.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="40.44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="15.11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="14.21"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="5" style="1" width="8.54"/>
+    <col min="1" max="1" width="31.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="40.44140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="14.21875" style="1" customWidth="1"/>
+    <col min="5" max="16384" width="8.5546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>104</v>
       </c>
@@ -2645,7 +2552,7 @@
       </c>
       <c r="D1" s="2"/>
     </row>
-    <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
@@ -2657,7 +2564,7 @@
       </c>
       <c r="D2" s="2"/>
     </row>
-    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -2669,7 +2576,7 @@
       </c>
       <c r="D3" s="2"/>
     </row>
-    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
@@ -2681,7 +2588,7 @@
       </c>
       <c r="D4" s="2"/>
     </row>
-    <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>2</v>
       </c>
@@ -2693,7 +2600,7 @@
       </c>
       <c r="D5" s="2"/>
     </row>
-    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>2</v>
       </c>
@@ -2705,7 +2612,7 @@
       </c>
       <c r="D6" s="2"/>
     </row>
-    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>2</v>
       </c>
@@ -2717,7 +2624,7 @@
       </c>
       <c r="D7" s="2"/>
     </row>
-    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>2</v>
       </c>
@@ -2729,7 +2636,7 @@
       </c>
       <c r="D8" s="2"/>
     </row>
-    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>2</v>
       </c>
@@ -2741,7 +2648,7 @@
       </c>
       <c r="D9" s="2"/>
     </row>
-    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>2</v>
       </c>
@@ -2753,7 +2660,7 @@
       </c>
       <c r="D10" s="2"/>
     </row>
-    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>2</v>
       </c>
@@ -2765,7 +2672,7 @@
       </c>
       <c r="D11" s="2"/>
     </row>
-    <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>2</v>
       </c>
@@ -2777,7 +2684,7 @@
       </c>
       <c r="D12" s="2"/>
     </row>
-    <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>2</v>
       </c>
@@ -2789,7 +2696,7 @@
       </c>
       <c r="D13" s="2"/>
     </row>
-    <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
         <v>2</v>
       </c>
@@ -2801,7 +2708,7 @@
       </c>
       <c r="D14" s="2"/>
     </row>
-    <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
         <v>2</v>
       </c>
@@ -2813,7 +2720,7 @@
       </c>
       <c r="D15" s="2"/>
     </row>
-    <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>2</v>
       </c>
@@ -2825,7 +2732,7 @@
       </c>
       <c r="D16" s="2"/>
     </row>
-    <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
         <v>2</v>
       </c>
@@ -2837,7 +2744,7 @@
       </c>
       <c r="D17" s="2"/>
     </row>
-    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="7" t="s">
         <v>31</v>
       </c>
@@ -2851,7 +2758,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>130</v>
       </c>
@@ -2865,7 +2772,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>133</v>
       </c>
@@ -2879,7 +2786,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>135</v>
       </c>
@@ -2893,7 +2800,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>137</v>
       </c>
@@ -2907,7 +2814,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>139</v>
       </c>
@@ -2921,7 +2828,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>141</v>
       </c>
@@ -2935,7 +2842,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
         <v>143</v>
       </c>
@@ -2949,7 +2856,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
         <v>145</v>
       </c>
@@ -2963,7 +2870,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
         <v>147</v>
       </c>
@@ -2977,7 +2884,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
         <v>149</v>
       </c>
@@ -2991,7 +2898,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
         <v>109</v>
       </c>
@@ -3005,7 +2912,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
         <v>152</v>
       </c>
@@ -3019,7 +2926,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
         <v>154</v>
       </c>
@@ -3033,7 +2940,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
         <v>156</v>
       </c>
@@ -3047,7 +2954,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
         <v>158</v>
       </c>
@@ -3061,7 +2968,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
         <v>160</v>
       </c>
@@ -3075,7 +2982,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
         <v>162</v>
       </c>
@@ -3089,7 +2996,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
         <v>164</v>
       </c>
@@ -3103,7 +3010,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
         <v>165</v>
       </c>
@@ -3117,7 +3024,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
         <v>167</v>
       </c>
@@ -3131,7 +3038,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
         <v>169</v>
       </c>
@@ -3145,7 +3052,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
         <v>171</v>
       </c>
@@ -3159,7 +3066,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
         <v>173</v>
       </c>
@@ -3173,7 +3080,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
         <v>175</v>
       </c>
@@ -3187,7 +3094,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
         <v>177</v>
       </c>
@@ -3201,7 +3108,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
         <v>179</v>
       </c>
@@ -3215,7 +3122,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
         <v>181</v>
       </c>
@@ -3229,7 +3136,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
         <v>183</v>
       </c>
@@ -3243,7 +3150,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
         <v>185</v>
       </c>
@@ -3257,7 +3164,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
         <v>187</v>
       </c>
@@ -3271,7 +3178,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
         <v>189</v>
       </c>
@@ -3285,7 +3192,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
         <v>191</v>
       </c>
@@ -3299,7 +3206,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
         <v>193</v>
       </c>
@@ -3313,7 +3220,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
         <v>195</v>
       </c>
@@ -3327,7 +3234,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
         <v>197</v>
       </c>
@@ -3341,7 +3248,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
         <v>199</v>
       </c>
@@ -3355,7 +3262,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
         <v>201</v>
       </c>
@@ -3369,7 +3276,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
         <v>203</v>
       </c>
@@ -3383,7 +3290,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
         <v>205</v>
       </c>
@@ -3397,7 +3304,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
         <v>207</v>
       </c>
@@ -3411,7 +3318,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
         <v>208</v>
       </c>
@@ -3425,7 +3332,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
         <v>210</v>
       </c>
@@ -3439,7 +3346,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
         <v>212</v>
       </c>
@@ -3453,7 +3360,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
         <v>214</v>
       </c>
@@ -3467,7 +3374,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
         <v>215</v>
       </c>
@@ -3481,7 +3388,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="65" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
         <v>217</v>
       </c>
@@ -3495,7 +3402,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="66" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
         <v>219</v>
       </c>
@@ -3509,7 +3416,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="67" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
         <v>221</v>
       </c>
@@ -3523,7 +3430,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="68" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
         <v>223</v>
       </c>
@@ -3537,7 +3444,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
         <v>225</v>
       </c>
@@ -3551,7 +3458,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="70" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
         <v>227</v>
       </c>
@@ -3565,7 +3472,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="71" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
         <v>228</v>
       </c>
@@ -3579,7 +3486,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="72" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
         <v>230</v>
       </c>
@@ -3593,7 +3500,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="73" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
         <v>232</v>
       </c>
@@ -3607,7 +3514,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="74" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
         <v>234</v>
       </c>
@@ -3621,7 +3528,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="75" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
         <v>236</v>
       </c>
@@ -3635,7 +3542,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="76" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
         <v>238</v>
       </c>
@@ -3649,7 +3556,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
         <v>240</v>
       </c>
@@ -3663,7 +3570,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="s">
         <v>242</v>
       </c>
@@ -3677,7 +3584,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="s">
         <v>244</v>
       </c>
@@ -3691,7 +3598,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="80" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
         <v>246</v>
       </c>
@@ -3705,7 +3612,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="81" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A81" s="1" t="s">
         <v>248</v>
       </c>
@@ -3719,7 +3626,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="82" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
         <v>250</v>
       </c>
@@ -3733,7 +3640,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="83" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A83" s="1" t="s">
         <v>252</v>
       </c>
@@ -3747,7 +3654,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="84" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A84" s="1" t="s">
         <v>254</v>
       </c>
@@ -3761,7 +3668,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="85" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A85" s="1" t="s">
         <v>256</v>
       </c>
@@ -3775,7 +3682,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="86" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A86" s="1" t="s">
         <v>258</v>
       </c>
@@ -3789,7 +3696,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="87" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A87" s="1" t="s">
         <v>260</v>
       </c>
@@ -3803,7 +3710,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="88" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A88" s="1" t="s">
         <v>262</v>
       </c>
@@ -3817,7 +3724,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="89" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A89" s="1" t="s">
         <v>263</v>
       </c>
@@ -3831,7 +3738,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="90" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A90" s="1" t="s">
         <v>265</v>
       </c>
@@ -3845,7 +3752,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="91" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A91" s="1" t="s">
         <v>267</v>
       </c>
@@ -3859,7 +3766,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="92" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A92" s="1" t="s">
         <v>269</v>
       </c>
@@ -3873,7 +3780,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="93" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A93" s="1" t="s">
         <v>271</v>
       </c>
@@ -3887,7 +3794,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="94" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A94" s="1" t="s">
         <v>273</v>
       </c>
@@ -3901,7 +3808,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="95" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A95" s="1" t="s">
         <v>275</v>
       </c>
@@ -3915,7 +3822,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="96" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A96" s="1" t="s">
         <v>277</v>
       </c>
@@ -3929,7 +3836,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="97" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A97" s="1" t="s">
         <v>279</v>
       </c>
@@ -3943,7 +3850,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="98" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A98" s="1" t="s">
         <v>280</v>
       </c>
@@ -3957,7 +3864,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="99" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A99" s="1" t="s">
         <v>282</v>
       </c>
@@ -3971,7 +3878,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="100" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A100" s="1" t="s">
         <v>284</v>
       </c>
@@ -3985,7 +3892,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="101" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A101" s="1" t="s">
         <v>286</v>
       </c>
@@ -3999,7 +3906,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="102" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A102" s="1" t="s">
         <v>288</v>
       </c>
@@ -4013,7 +3920,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="103" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A103" s="1" t="s">
         <v>290</v>
       </c>
@@ -4027,7 +3934,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="104" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A104" s="1" t="s">
         <v>292</v>
       </c>
@@ -4041,7 +3948,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="105" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="105" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A105" s="1" t="s">
         <v>294</v>
       </c>
@@ -4055,7 +3962,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="106" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A106" s="1" t="s">
         <v>296</v>
       </c>
@@ -4069,7 +3976,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="107" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="107" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A107" s="1" t="s">
         <v>298</v>
       </c>
@@ -4083,7 +3990,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="108" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="108" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A108" s="1" t="s">
         <v>299</v>
       </c>
@@ -4097,7 +4004,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="109" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="109" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A109" s="1" t="s">
         <v>301</v>
       </c>
@@ -4111,7 +4018,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="110" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="110" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A110" s="1" t="s">
         <v>303</v>
       </c>
@@ -4125,7 +4032,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="111" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A111" s="1" t="s">
         <v>305</v>
       </c>
@@ -4139,7 +4046,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="112" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="112" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A112" s="1" t="s">
         <v>307</v>
       </c>
@@ -4153,7 +4060,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="113" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="113" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A113" s="1" t="s">
         <v>309</v>
       </c>
@@ -4167,7 +4074,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="114" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="114" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A114" s="1" t="s">
         <v>311</v>
       </c>
@@ -4181,7 +4088,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="115" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="115" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A115" s="1" t="s">
         <v>313</v>
       </c>
@@ -4195,7 +4102,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="116" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="116" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A116" s="1" t="s">
         <v>315</v>
       </c>
@@ -4209,7 +4116,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="117" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="117" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A117" s="1" t="s">
         <v>317</v>
       </c>
@@ -4223,7 +4130,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="118" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="118" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A118" s="1" t="s">
         <v>319</v>
       </c>
@@ -4237,7 +4144,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="119" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="119" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A119" s="1" t="s">
         <v>321</v>
       </c>
@@ -4251,7 +4158,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="120" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="120" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A120" s="1" t="s">
         <v>323</v>
       </c>
@@ -4265,7 +4172,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="121" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="121" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A121" s="1" t="s">
         <v>325</v>
       </c>
@@ -4279,7 +4186,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="122" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="122" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A122" s="1" t="s">
         <v>327</v>
       </c>
@@ -4293,7 +4200,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="123" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="123" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A123" s="1" t="s">
         <v>329</v>
       </c>
@@ -4307,7 +4214,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="124" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="124" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A124" s="1" t="s">
         <v>331</v>
       </c>
@@ -4321,7 +4228,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="125" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="125" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A125" s="1" t="s">
         <v>333</v>
       </c>
@@ -4335,7 +4242,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="126" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="126" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A126" s="1" t="s">
         <v>335</v>
       </c>
@@ -4349,7 +4256,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="127" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="127" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A127" s="1" t="s">
         <v>337</v>
       </c>
@@ -4363,7 +4270,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="128" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="128" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A128" s="1" t="s">
         <v>339</v>
       </c>
@@ -4377,7 +4284,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="129" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="129" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A129" s="1" t="s">
         <v>341</v>
       </c>
@@ -4391,7 +4298,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="130" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="130" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A130" s="1" t="s">
         <v>343</v>
       </c>
@@ -4405,7 +4312,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="131" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="131" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A131" s="1" t="s">
         <v>345</v>
       </c>
@@ -4419,7 +4326,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="132" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="132" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A132" s="1" t="s">
         <v>347</v>
       </c>
@@ -4433,7 +4340,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="133" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="133" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A133" s="1" t="s">
         <v>349</v>
       </c>
@@ -4447,7 +4354,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="134" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="134" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A134" s="1" t="s">
         <v>351</v>
       </c>
@@ -4461,7 +4368,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="135" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="135" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A135" s="1" t="s">
         <v>353</v>
       </c>
@@ -4475,7 +4382,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="136" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="136" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A136" s="1" t="s">
         <v>355</v>
       </c>
@@ -4489,7 +4396,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="137" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="137" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A137" s="1" t="s">
         <v>357</v>
       </c>
@@ -4503,7 +4410,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="138" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="138" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A138" s="1" t="s">
         <v>359</v>
       </c>
@@ -4517,7 +4424,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="139" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="139" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A139" s="1" t="s">
         <v>361</v>
       </c>
@@ -4531,7 +4438,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="140" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="140" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A140" s="1" t="s">
         <v>363</v>
       </c>
@@ -4545,7 +4452,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="141" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="141" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A141" s="1" t="s">
         <v>365</v>
       </c>
@@ -4559,7 +4466,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="142" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="142" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A142" s="1" t="s">
         <v>367</v>
       </c>
@@ -4573,7 +4480,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="143" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="143" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A143" s="1" t="s">
         <v>369</v>
       </c>
@@ -4587,7 +4494,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="144" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="144" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A144" s="1" t="s">
         <v>371</v>
       </c>
@@ -4601,7 +4508,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="145" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="145" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A145" s="1" t="s">
         <v>373</v>
       </c>
@@ -4615,7 +4522,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="146" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="146" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A146" s="1" t="s">
         <v>375</v>
       </c>
@@ -4629,7 +4536,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="147" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="147" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A147" s="1" t="s">
         <v>377</v>
       </c>
@@ -4643,7 +4550,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="148" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="148" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A148" s="1" t="s">
         <v>379</v>
       </c>
@@ -4657,7 +4564,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="149" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="149" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A149" s="1" t="s">
         <v>381</v>
       </c>
@@ -4671,7 +4578,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="150" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="150" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A150" s="1" t="s">
         <v>383</v>
       </c>
@@ -4685,7 +4592,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="151" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="151" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A151" s="1" t="s">
         <v>385</v>
       </c>
@@ -4699,7 +4606,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="152" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="152" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A152" s="1" t="s">
         <v>387</v>
       </c>
@@ -4713,7 +4620,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="153" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="153" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A153" s="1" t="s">
         <v>389</v>
       </c>
@@ -4727,7 +4634,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="154" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="154" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A154" s="1" t="s">
         <v>391</v>
       </c>
@@ -4741,7 +4648,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="155" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="155" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A155" s="1" t="s">
         <v>393</v>
       </c>
@@ -4755,7 +4662,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="156" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="156" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A156" s="1" t="s">
         <v>395</v>
       </c>
@@ -4769,7 +4676,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="157" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="157" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A157" s="1" t="s">
         <v>397</v>
       </c>
@@ -4783,7 +4690,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="158" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="158" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A158" s="1" t="s">
         <v>399</v>
       </c>
@@ -4797,7 +4704,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="159" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="159" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A159" s="1" t="s">
         <v>401</v>
       </c>
@@ -4812,32 +4719,24 @@
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:D18"/>
-  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.25" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.5546875" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="43.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="38.44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="15.11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="13.34"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="5" style="1" width="8.54"/>
+    <col min="1" max="1" width="43.88671875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="38.44140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="13.33203125" style="1" customWidth="1"/>
+    <col min="5" max="16384" width="8.5546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>104</v>
       </c>
@@ -4846,7 +4745,7 @@
       </c>
       <c r="D1" s="2"/>
     </row>
-    <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
@@ -4858,7 +4757,7 @@
       </c>
       <c r="D2" s="2"/>
     </row>
-    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -4870,7 +4769,7 @@
       </c>
       <c r="D3" s="2"/>
     </row>
-    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
@@ -4882,7 +4781,7 @@
       </c>
       <c r="D4" s="2"/>
     </row>
-    <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>2</v>
       </c>
@@ -4894,7 +4793,7 @@
       </c>
       <c r="D5" s="2"/>
     </row>
-    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>2</v>
       </c>
@@ -4906,7 +4805,7 @@
       </c>
       <c r="D6" s="2"/>
     </row>
-    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>2</v>
       </c>
@@ -4918,7 +4817,7 @@
       </c>
       <c r="D7" s="2"/>
     </row>
-    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>2</v>
       </c>
@@ -4930,7 +4829,7 @@
       </c>
       <c r="D8" s="2"/>
     </row>
-    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>2</v>
       </c>
@@ -4942,7 +4841,7 @@
       </c>
       <c r="D9" s="2"/>
     </row>
-    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>2</v>
       </c>
@@ -4954,7 +4853,7 @@
       </c>
       <c r="D10" s="2"/>
     </row>
-    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>2</v>
       </c>
@@ -4966,7 +4865,7 @@
       </c>
       <c r="D11" s="2"/>
     </row>
-    <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>2</v>
       </c>
@@ -4978,10 +4877,10 @@
       </c>
       <c r="D12" s="2"/>
     </row>
-    <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="D13" s="2"/>
     </row>
-    <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
         <v>31</v>
       </c>
@@ -4992,7 +4891,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>55</v>
       </c>
@@ -5003,7 +4902,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>110</v>
       </c>
@@ -5014,7 +4913,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>113</v>
       </c>
@@ -5025,7 +4924,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>71</v>
       </c>
@@ -5037,32 +4936,24 @@
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:D21"/>
-  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.25" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.5546875" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="67.44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="35.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="15.11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="13.34"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="5" style="1" width="8.54"/>
+    <col min="1" max="1" width="67.44140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="35.33203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="13.33203125" style="1" customWidth="1"/>
+    <col min="5" max="16384" width="8.5546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>104</v>
       </c>
@@ -5071,7 +4962,7 @@
       </c>
       <c r="D1" s="2"/>
     </row>
-    <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
@@ -5083,7 +4974,7 @@
       </c>
       <c r="D2" s="2"/>
     </row>
-    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -5095,7 +4986,7 @@
       </c>
       <c r="D3" s="2"/>
     </row>
-    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
@@ -5107,7 +4998,7 @@
       </c>
       <c r="D4" s="2"/>
     </row>
-    <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>2</v>
       </c>
@@ -5119,7 +5010,7 @@
       </c>
       <c r="D5" s="2"/>
     </row>
-    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>2</v>
       </c>
@@ -5131,7 +5022,7 @@
       </c>
       <c r="D6" s="2"/>
     </row>
-    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>2</v>
       </c>
@@ -5143,7 +5034,7 @@
       </c>
       <c r="D7" s="2"/>
     </row>
-    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>2</v>
       </c>
@@ -5155,7 +5046,7 @@
       </c>
       <c r="D8" s="2"/>
     </row>
-    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>2</v>
       </c>
@@ -5167,7 +5058,7 @@
       </c>
       <c r="D9" s="2"/>
     </row>
-    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>2</v>
       </c>
@@ -5179,7 +5070,7 @@
       </c>
       <c r="D10" s="2"/>
     </row>
-    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>2</v>
       </c>
@@ -5191,7 +5082,7 @@
       </c>
       <c r="D11" s="2"/>
     </row>
-    <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>2</v>
       </c>
@@ -5203,10 +5094,10 @@
       </c>
       <c r="D12" s="2"/>
     </row>
-    <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="D13" s="2"/>
     </row>
-    <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
         <v>31</v>
       </c>
@@ -5214,7 +5105,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>58</v>
       </c>
@@ -5222,7 +5113,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>67</v>
       </c>
@@ -5230,7 +5121,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>74</v>
       </c>
@@ -5238,7 +5129,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>80</v>
       </c>
@@ -5246,7 +5137,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>86</v>
       </c>
@@ -5254,7 +5145,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>93</v>
       </c>
@@ -5262,7 +5153,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>100</v>
       </c>
@@ -5271,32 +5162,24 @@
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:D16"/>
-  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.25" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.5546875" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="25.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="14.44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="62.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="13.34"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="5" style="1" width="8.54"/>
+    <col min="1" max="1" width="25.33203125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="14.44140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="62.33203125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="13.33203125" style="1" customWidth="1"/>
+    <col min="5" max="16384" width="8.5546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>104</v>
       </c>
@@ -5305,7 +5188,7 @@
       </c>
       <c r="D1" s="2"/>
     </row>
-    <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
@@ -5317,7 +5200,7 @@
       </c>
       <c r="D2" s="2"/>
     </row>
-    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -5329,7 +5212,7 @@
       </c>
       <c r="D3" s="2"/>
     </row>
-    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
@@ -5341,7 +5224,7 @@
       </c>
       <c r="D4" s="2"/>
     </row>
-    <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>2</v>
       </c>
@@ -5353,7 +5236,7 @@
       </c>
       <c r="D5" s="2"/>
     </row>
-    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>2</v>
       </c>
@@ -5365,7 +5248,7 @@
       </c>
       <c r="D6" s="2"/>
     </row>
-    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>2</v>
       </c>
@@ -5377,7 +5260,7 @@
       </c>
       <c r="D7" s="2"/>
     </row>
-    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>2</v>
       </c>
@@ -5389,7 +5272,7 @@
       </c>
       <c r="D8" s="2"/>
     </row>
-    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>2</v>
       </c>
@@ -5401,7 +5284,7 @@
       </c>
       <c r="D9" s="2"/>
     </row>
-    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>2</v>
       </c>
@@ -5413,7 +5296,7 @@
       </c>
       <c r="D10" s="2"/>
     </row>
-    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>2</v>
       </c>
@@ -5425,7 +5308,7 @@
       </c>
       <c r="D11" s="2"/>
     </row>
-    <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>2</v>
       </c>
@@ -5437,10 +5320,10 @@
       </c>
       <c r="D12" s="2"/>
     </row>
-    <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="D13" s="2"/>
     </row>
-    <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
         <v>31</v>
       </c>
@@ -5448,7 +5331,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>112</v>
       </c>
@@ -5456,7 +5339,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>116</v>
       </c>
@@ -5465,34 +5348,26 @@
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:F23"/>
-  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.25" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.5546875" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="47"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="27"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="29.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="67.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="25.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="20.56"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="7" style="1" width="8.54"/>
+    <col min="1" max="1" width="47" style="1" customWidth="1"/>
+    <col min="2" max="2" width="27" style="1" customWidth="1"/>
+    <col min="3" max="3" width="29.88671875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="67.33203125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="25.33203125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="20.5546875" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="8.5546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>104</v>
       </c>
@@ -5501,7 +5376,7 @@
       </c>
       <c r="D1" s="2"/>
     </row>
-    <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
@@ -5513,7 +5388,7 @@
       </c>
       <c r="D2" s="2"/>
     </row>
-    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -5525,7 +5400,7 @@
       </c>
       <c r="D3" s="2"/>
     </row>
-    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
@@ -5537,7 +5412,7 @@
       </c>
       <c r="D4" s="2"/>
     </row>
-    <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>2</v>
       </c>
@@ -5549,7 +5424,7 @@
       </c>
       <c r="D5" s="2"/>
     </row>
-    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>2</v>
       </c>
@@ -5561,7 +5436,7 @@
       </c>
       <c r="D6" s="2"/>
     </row>
-    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>2</v>
       </c>
@@ -5573,7 +5448,7 @@
       </c>
       <c r="D7" s="2"/>
     </row>
-    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>2</v>
       </c>
@@ -5585,7 +5460,7 @@
       </c>
       <c r="D8" s="2"/>
     </row>
-    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>2</v>
       </c>
@@ -5597,7 +5472,7 @@
       </c>
       <c r="D9" s="2"/>
     </row>
-    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>2</v>
       </c>
@@ -5609,7 +5484,7 @@
       </c>
       <c r="D10" s="2"/>
     </row>
-    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>2</v>
       </c>
@@ -5621,7 +5496,7 @@
       </c>
       <c r="D11" s="2"/>
     </row>
-    <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>2</v>
       </c>
@@ -5633,7 +5508,7 @@
       </c>
       <c r="D12" s="2"/>
     </row>
-    <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>2</v>
       </c>
@@ -5645,7 +5520,7 @@
       </c>
       <c r="D13" s="2"/>
     </row>
-    <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
         <v>2</v>
       </c>
@@ -5657,7 +5532,7 @@
       </c>
       <c r="D14" s="2"/>
     </row>
-    <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
         <v>31</v>
       </c>
@@ -5677,7 +5552,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>57</v>
       </c>
@@ -5697,7 +5572,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>66</v>
       </c>
@@ -5717,7 +5592,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>73</v>
       </c>
@@ -5737,7 +5612,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>79</v>
       </c>
@@ -5757,7 +5632,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>85</v>
       </c>
@@ -5777,7 +5652,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>92</v>
       </c>
@@ -5797,7 +5672,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>99</v>
       </c>
@@ -5818,32 +5693,24 @@
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:D19"/>
-  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.25" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.5546875" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="83.44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="48.11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="62.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="38.56"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="5" style="1" width="8.54"/>
+    <col min="1" max="1" width="83.44140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="48.109375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="62.33203125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="38.5546875" style="1" customWidth="1"/>
+    <col min="5" max="16384" width="8.5546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>104</v>
       </c>
@@ -5851,7 +5718,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
@@ -5862,7 +5729,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -5873,7 +5740,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
@@ -5884,7 +5751,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>2</v>
       </c>
@@ -5895,7 +5762,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>2</v>
       </c>
@@ -5906,7 +5773,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>2</v>
       </c>
@@ -5917,7 +5784,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>2</v>
       </c>
@@ -5928,7 +5795,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>2</v>
       </c>
@@ -5939,7 +5806,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>2</v>
       </c>
@@ -5950,7 +5817,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>2</v>
       </c>
@@ -5961,7 +5828,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>2</v>
       </c>
@@ -5972,7 +5839,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>2</v>
       </c>
@@ -5983,7 +5850,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
         <v>31</v>
       </c>
@@ -5997,37 +5864,37 @@
         <v>428</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>60</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>343</v>
       </c>
-      <c r="C16" s="11"/>
-      <c r="D16" s="11"/>
-    </row>
-    <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C16" s="10"/>
+      <c r="D16" s="10"/>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>418</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>343</v>
       </c>
-      <c r="C17" s="12"/>
-      <c r="D17" s="12"/>
-    </row>
-    <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C17" s="11"/>
+      <c r="D17" s="11"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>417</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>343</v>
       </c>
-      <c r="C18" s="11"/>
-      <c r="D18" s="11"/>
-    </row>
-    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C18" s="10"/>
+      <c r="D18" s="10"/>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>429</v>
       </c>
@@ -6036,13 +5903,8 @@
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
@@ -6055,277 +5917,10 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010024F51093868FB24EBD35CDAFD175069E" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="84be37977f167f33bd3126630a183308">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="fe920753-c448-4b18-b0e8-18b73856b91a" xmlns:ns3="127cd07f-9ffd-4ce8-b21a-e01c9ecdfd33" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="468d2d265cee29b3ccbe510123b8323a" ns2:_="" ns3:_="">
-    <xsd:import namespace="fe920753-c448-4b18-b0e8-18b73856b91a"/>
-    <xsd:import namespace="127cd07f-9ffd-4ce8-b21a-e01c9ecdfd33"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:Links" minOccurs="0"/>
-                <xsd:element ref="ns2:_Flow_SignoffStatus" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceBillingMetadata" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="fe920753-c448-4b18-b0e8-18b73856b91a" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="Links" ma:index="8" nillable="true" ma:displayName="Links" ma:list="{a7ac44d4-7c1b-4777-b230-e6cff6938442}" ma:internalName="Links" ma:readOnly="true" ma:showField="From_x0020_Document">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Lookup"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="_Flow_SignoffStatus" ma:index="9" nillable="true" ma:displayName="Sign Off" ma:internalName="SignOff">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceMetadata" ma:index="10" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="11" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="12" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="13" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="15" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="47bde53e-b0a2-4e98-8550-8a152603f3a2" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="17" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="18" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="19" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="20" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="21" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceBillingMetadata" ma:index="22" nillable="true" ma:displayName="MediaServiceBillingMetadata" ma:hidden="true" ma:internalName="MediaServiceBillingMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="127cd07f-9ffd-4ce8-b21a-e01c9ecdfd33" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="TaxCatchAll" ma:index="16" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{b0f5931e-afe6-4408-8af1-48b0e6c2bd75}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="127cd07f-9ffd-4ce8-b21a-e01c9ecdfd33">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_Flow_SignoffStatus xmlns="fe920753-c448-4b18-b0e8-18b73856b91a" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="fe920753-c448-4b18-b0e8-18b73856b91a">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="127cd07f-9ffd-4ce8-b21a-e01c9ecdfd33" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D9A6A36E-DDA5-4D61-81B4-BE56B2BC85AF}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{71A7481B-B3C3-451C-BC28-8D07A1B6586A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="fe920753-c448-4b18-b0e8-18b73856b91a"/>
-    <ds:schemaRef ds:uri="127cd07f-9ffd-4ce8-b21a-e01c9ecdfd33"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{90095A14-373E-46B8-A609-CE77E7041A80}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="fe920753-c448-4b18-b0e8-18b73856b91a"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="127cd07f-9ffd-4ce8-b21a-e01c9ecdfd33"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>